--- a/artfynd/A 51118-2024 artfynd.xlsx
+++ b/artfynd/A 51118-2024 artfynd.xlsx
@@ -1126,7 +1126,7 @@
         <v>121149764</v>
       </c>
       <c r="B6" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 51118-2024 artfynd.xlsx
+++ b/artfynd/A 51118-2024 artfynd.xlsx
@@ -1126,7 +1126,7 @@
         <v>121149764</v>
       </c>
       <c r="B6" t="n">
-        <v>92008</v>
+        <v>92020</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 51118-2024 artfynd.xlsx
+++ b/artfynd/A 51118-2024 artfynd.xlsx
@@ -1126,7 +1126,7 @@
         <v>121149764</v>
       </c>
       <c r="B6" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 51118-2024 artfynd.xlsx
+++ b/artfynd/A 51118-2024 artfynd.xlsx
@@ -1126,7 +1126,7 @@
         <v>121149764</v>
       </c>
       <c r="B6" t="n">
-        <v>92021</v>
+        <v>92024</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 51118-2024 artfynd.xlsx
+++ b/artfynd/A 51118-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1232,6 +1232,103 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126119349</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hangaslamm, Hangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>484085</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6842865</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51118-2024 artfynd.xlsx
+++ b/artfynd/A 51118-2024 artfynd.xlsx
@@ -1237,7 +1237,7 @@
         <v>126119349</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51118-2024 artfynd.xlsx
+++ b/artfynd/A 51118-2024 artfynd.xlsx
@@ -1237,7 +1237,7 @@
         <v>126119349</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51118-2024 artfynd.xlsx
+++ b/artfynd/A 51118-2024 artfynd.xlsx
@@ -1237,7 +1237,7 @@
         <v>126119349</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51118-2024 artfynd.xlsx
+++ b/artfynd/A 51118-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109910315</v>
+        <v>112610715</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484131.5761105471</v>
+        <v>484131</v>
       </c>
       <c r="R2" t="n">
-        <v>6842797.943926304</v>
+        <v>6842798</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2023-05-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-05-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,53 +777,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109910314</v>
+        <v>121149764</v>
       </c>
       <c r="B3" t="n">
-        <v>107952</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221049</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Valeriana dioica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tandsjöborg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484136.3399522842</v>
+        <v>484091</v>
       </c>
       <c r="R3" t="n">
-        <v>6842801.24096984</v>
+        <v>6842813</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,27 +846,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,37 +883,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112610715</v>
+        <v>112610714</v>
       </c>
       <c r="B4" t="n">
-        <v>89791</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484132</v>
+        <v>484136</v>
       </c>
       <c r="R4" t="n">
-        <v>6842798</v>
+        <v>6842801</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,19 +985,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112610714</v>
+        <v>126119349</v>
       </c>
       <c r="B5" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1052,17 +1016,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tandsjöborg, Dlr</t>
+          <t>Hangaslamm, Hangaslamm, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484136</v>
+        <v>484085</v>
       </c>
       <c r="R5" t="n">
-        <v>6842801</v>
+        <v>6842865</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,17 +1050,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,69 +1070,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121149764</v>
+        <v>126119487</v>
       </c>
       <c r="B6" t="n">
-        <v>92024</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tandsjöborg, Dlr</t>
+          <t>Röstmyran, Röstmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484091</v>
+        <v>484158</v>
       </c>
       <c r="R6" t="n">
-        <v>6842813</v>
+        <v>6842946</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,17 +1147,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,57 +1167,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126119349</v>
+        <v>126119471</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hangaslamm, Hangaslamm, Dlr</t>
+          <t>Röstmyran, Röstmyran, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484085</v>
+        <v>484174</v>
       </c>
       <c r="R7" t="n">
-        <v>6842865</v>
+        <v>6842940</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 51118-2024 artfynd.xlsx
+++ b/artfynd/A 51118-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610715</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149764</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610714</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126119349</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1176,6 +1201,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126119487</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1273,8 +1303,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126119471</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>